--- a/data/dataframe/10077.xlsx
+++ b/data/dataframe/10077.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tug83224/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shujie/jlab/CJ/CJ-database/data/dataframe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D647DDE8-FD23-544E-ADEA-A678AD8FFC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAA51E5-CC84-C649-9110-F82ABF2F789C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="1080" windowWidth="30720" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="format" sheetId="2" r:id="rId1"/>
@@ -92,9 +92,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>Jlab-E06-009</t>
-  </si>
-  <si>
     <t>d</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>exp</t>
+  </si>
+  <si>
+    <t>JLab-E06-009</t>
   </si>
 </sst>
 </file>
@@ -502,7 +502,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>0.71</v>
@@ -552,10 +552,10 @@
         <v>0.97501000000000004</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>1.8945500000000001E-2</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>0.75</v>
@@ -587,10 +587,10 @@
         <v>0.99631999999999998</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>2.7941000000000001E-2</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0.79</v>
@@ -622,10 +622,10 @@
         <v>1.0176000000000001</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <v>4.2755500000000002E-2</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0.83</v>
@@ -657,10 +657,10 @@
         <v>1.0389999999999999</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5">
         <v>5.4635000000000003E-2</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0.87</v>
@@ -692,10 +692,10 @@
         <v>1.0603</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <v>6.5024999999999999E-2</v>
@@ -712,7 +712,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0.91</v>
@@ -727,10 +727,10 @@
         <v>1.0815999999999999</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7">
         <v>6.4604999999999996E-2</v>
@@ -747,7 +747,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0.95</v>
@@ -762,10 +762,10 @@
         <v>1.1029</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8">
         <v>5.7404999999999998E-2</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>0.99</v>
@@ -797,10 +797,10 @@
         <v>1.1242000000000001</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9">
         <v>4.5992999999999999E-2</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>1.03</v>
@@ -832,10 +832,10 @@
         <v>1.1455</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10">
         <v>3.6926500000000001E-2</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>1.07</v>
@@ -867,10 +867,10 @@
         <v>1.1668000000000001</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11">
         <v>3.1242499999999999E-2</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>1.1100000000000001</v>
@@ -902,10 +902,10 @@
         <v>1.1881999999999999</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12">
         <v>2.7316500000000001E-2</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>1.1499999999999999</v>
@@ -937,10 +937,10 @@
         <v>1.2095</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13">
         <v>2.5724500000000001E-2</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>1.19</v>
@@ -972,10 +972,10 @@
         <v>1.2307999999999999</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H14">
         <v>2.6227E-2</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>1.23</v>
@@ -1007,10 +1007,10 @@
         <v>1.2521</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H15">
         <v>2.8334999999999999E-2</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>1.27</v>
@@ -1042,10 +1042,10 @@
         <v>1.2734000000000001</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16">
         <v>3.1756E-2</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>1.31</v>
@@ -1077,10 +1077,10 @@
         <v>1.2947</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17">
         <v>3.6718000000000001E-2</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>1.35</v>
@@ -1112,10 +1112,10 @@
         <v>1.3161</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18">
         <v>4.1385999999999999E-2</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>1.39</v>
@@ -1147,10 +1147,10 @@
         <v>1.3373999999999999</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19">
         <v>4.7389000000000001E-2</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>1.43</v>
@@ -1182,10 +1182,10 @@
         <v>1.3587</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20">
         <v>5.1995E-2</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>1.47</v>
@@ -1217,10 +1217,10 @@
         <v>1.38</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21">
         <v>5.6515000000000003E-2</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>1.51</v>
@@ -1252,10 +1252,10 @@
         <v>1.4013</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22">
         <v>6.0100000000000001E-2</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>1.55</v>
@@ -1287,10 +1287,10 @@
         <v>1.4226000000000001</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H23">
         <v>6.2045000000000003E-2</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>1.59</v>
@@ -1322,10 +1322,10 @@
         <v>1.444</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24">
         <v>6.2280000000000002E-2</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>1.63</v>
@@ -1357,10 +1357,10 @@
         <v>1.4653</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25">
         <v>6.3320000000000001E-2</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>1.67</v>
@@ -1392,10 +1392,10 @@
         <v>1.4865999999999999</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H26">
         <v>6.3579999999999998E-2</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>1.71</v>
@@ -1427,10 +1427,10 @@
         <v>1.5079</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27">
         <v>6.5475000000000005E-2</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B28">
         <v>1.75</v>
@@ -1462,10 +1462,10 @@
         <v>1.5291999999999999</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H28">
         <v>6.5634999999999999E-2</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>1.79</v>
@@ -1497,10 +1497,10 @@
         <v>1.5505</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29">
         <v>6.7184999999999995E-2</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>1.83</v>
@@ -1532,10 +1532,10 @@
         <v>1.5718000000000001</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30">
         <v>6.9519999999999998E-2</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>1.87</v>
@@ -1567,10 +1567,10 @@
         <v>1.5931999999999999</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H31">
         <v>7.2069999999999995E-2</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B32">
         <v>1.91</v>
@@ -1602,10 +1602,10 @@
         <v>1.6145</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H32">
         <v>7.4365000000000001E-2</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B33">
         <v>1.95</v>
@@ -1637,10 +1637,10 @@
         <v>1.6357999999999999</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H33">
         <v>7.8200000000000006E-2</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34">
         <v>1.99</v>
@@ -1672,10 +1672,10 @@
         <v>1.6571</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H34">
         <v>8.1335000000000005E-2</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B35">
         <v>2.0299999999999998</v>
@@ -1707,10 +1707,10 @@
         <v>1.6783999999999999</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H35">
         <v>8.5235000000000005E-2</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>2.0699999999999998</v>
@@ -1742,10 +1742,10 @@
         <v>1.6997</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H36">
         <v>0.09</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B37">
         <v>2.11</v>
@@ -1777,10 +1777,10 @@
         <v>1.7211000000000001</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37">
         <v>9.4829999999999998E-2</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B38">
         <v>2.15</v>
@@ -1812,10 +1812,10 @@
         <v>1.7423999999999999</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H38">
         <v>9.9074999999999996E-2</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B39">
         <v>2.19</v>
@@ -1847,10 +1847,10 @@
         <v>1.7637</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H39">
         <v>0.10337499999999999</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B40">
         <v>2.23</v>
@@ -1882,10 +1882,10 @@
         <v>1.7849999999999999</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H40">
         <v>0.108025</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B41">
         <v>2.27</v>
@@ -1917,10 +1917,10 @@
         <v>1.8063</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H41">
         <v>0.11307</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B42">
         <v>2.31</v>
@@ -1952,10 +1952,10 @@
         <v>1.8275999999999999</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H42">
         <v>0.113875</v>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B43">
         <v>2.35</v>
@@ -1987,10 +1987,10 @@
         <v>1.849</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H43">
         <v>0.116845</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B44">
         <v>2.39</v>
@@ -2022,10 +2022,10 @@
         <v>1.8703000000000001</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H44">
         <v>0.11983000000000001</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B45">
         <v>2.4300000000000002</v>
@@ -2057,10 +2057,10 @@
         <v>1.8915999999999999</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H45">
         <v>0.1201</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B46">
         <v>2.4700000000000002</v>
@@ -2092,10 +2092,10 @@
         <v>1.9129</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H46">
         <v>0.12274</v>
@@ -2112,7 +2112,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B47">
         <v>2.5099999999999998</v>
@@ -2127,10 +2127,10 @@
         <v>1.9341999999999999</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H47">
         <v>0.12559500000000001</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B48">
         <v>2.5499999999999998</v>
@@ -2162,10 +2162,10 @@
         <v>1.9555</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H48">
         <v>0.12890499999999999</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B49">
         <v>2.59</v>
@@ -2197,10 +2197,10 @@
         <v>1.9767999999999999</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H49">
         <v>0.131275</v>
@@ -2217,7 +2217,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B50">
         <v>2.63</v>
@@ -2232,10 +2232,10 @@
         <v>1.9982</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H50">
         <v>0.13649</v>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>2.67</v>
@@ -2267,10 +2267,10 @@
         <v>2.0194999999999999</v>
       </c>
       <c r="F51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H51">
         <v>0.13933499999999999</v>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B52">
         <v>2.71</v>
@@ -2302,10 +2302,10 @@
         <v>2.0407999999999999</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H52">
         <v>0.14346</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B53">
         <v>2.75</v>
@@ -2337,10 +2337,10 @@
         <v>2.0621</v>
       </c>
       <c r="F53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H53">
         <v>0.14905499999999999</v>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B54">
         <v>2.79</v>
@@ -2372,10 +2372,10 @@
         <v>2.0834000000000001</v>
       </c>
       <c r="F54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H54">
         <v>0.15109</v>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B55">
         <v>2.83</v>
@@ -2407,10 +2407,10 @@
         <v>2.1046999999999998</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H55">
         <v>0.156525</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B56">
         <v>2.87</v>
@@ -2442,10 +2442,10 @@
         <v>2.1261000000000001</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H56">
         <v>0.15721499999999999</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B57">
         <v>2.91</v>
@@ -2477,10 +2477,10 @@
         <v>2.1474000000000002</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H57">
         <v>0.16261</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B58">
         <v>2.95</v>
@@ -2512,10 +2512,10 @@
         <v>2.1686999999999999</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H58">
         <v>0.16409000000000001</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B59">
         <v>2.99</v>
@@ -2547,10 +2547,10 @@
         <v>2.19</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H59">
         <v>0.16469500000000001</v>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B60">
         <v>3.03</v>
@@ -2582,10 +2582,10 @@
         <v>2.2113</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H60">
         <v>0.16685</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B61">
         <v>3.07</v>
@@ -2617,10 +2617,10 @@
         <v>2.2326000000000001</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H61">
         <v>0.16600999999999999</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B62">
         <v>3.11</v>
@@ -2652,10 +2652,10 @@
         <v>2.254</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H62">
         <v>0.168045</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B63">
         <v>3.15</v>
@@ -2687,10 +2687,10 @@
         <v>2.2753000000000001</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H63">
         <v>0.17078499999999999</v>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B64">
         <v>3.19</v>
@@ -2722,10 +2722,10 @@
         <v>2.2966000000000002</v>
       </c>
       <c r="F64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H64">
         <v>0.17088500000000001</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B65">
         <v>3.23</v>
@@ -2757,10 +2757,10 @@
         <v>2.3178999999999998</v>
       </c>
       <c r="F65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H65">
         <v>0.174815</v>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B66">
         <v>3.27</v>
@@ -2792,10 +2792,10 @@
         <v>2.3391999999999999</v>
       </c>
       <c r="F66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H66">
         <v>0.178145</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B67">
         <v>3.31</v>
@@ -2827,10 +2827,10 @@
         <v>2.3605</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H67">
         <v>0.177065</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B68">
         <v>3.35</v>
@@ -2862,10 +2862,10 @@
         <v>2.3818000000000001</v>
       </c>
       <c r="F68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H68">
         <v>0.18132000000000001</v>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B69">
         <v>3.39</v>
@@ -2897,10 +2897,10 @@
         <v>2.4032</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H69">
         <v>0.18493000000000001</v>
@@ -2917,7 +2917,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B70">
         <v>3.43</v>
@@ -2932,10 +2932,10 @@
         <v>2.4245000000000001</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H70">
         <v>0.18492</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B71">
         <v>3.47</v>
@@ -2967,10 +2967,10 @@
         <v>2.4458000000000002</v>
       </c>
       <c r="F71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H71">
         <v>0.190495</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B72">
         <v>3.51</v>
@@ -3002,10 +3002,10 @@
         <v>2.4670999999999998</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H72">
         <v>0.189525</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B73">
         <v>3.55</v>
@@ -3037,10 +3037,10 @@
         <v>2.4883999999999999</v>
       </c>
       <c r="F73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H73">
         <v>0.194685</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B74">
         <v>3.59</v>
@@ -3072,10 +3072,10 @@
         <v>2.5097</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H74">
         <v>0.19477</v>
@@ -3092,7 +3092,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B75">
         <v>3.63</v>
@@ -3107,10 +3107,10 @@
         <v>2.5310999999999999</v>
       </c>
       <c r="F75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H75">
         <v>0.19822000000000001</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B76">
         <v>3.67</v>
@@ -3142,10 +3142,10 @@
         <v>2.5524</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H76">
         <v>0.19983500000000001</v>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B77">
         <v>3.71</v>
@@ -3177,10 +3177,10 @@
         <v>2.5737000000000001</v>
       </c>
       <c r="F77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H77">
         <v>0.19808999999999999</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B78">
         <v>3.75</v>
@@ -3212,10 +3212,10 @@
         <v>2.5950000000000002</v>
       </c>
       <c r="F78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H78">
         <v>0.20538000000000001</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B79">
         <v>3.79</v>
@@ -3247,10 +3247,10 @@
         <v>2.6162999999999998</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H79">
         <v>0.20852000000000001</v>
@@ -3267,7 +3267,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B80">
         <v>3.83</v>
@@ -3282,10 +3282,10 @@
         <v>2.6375999999999999</v>
       </c>
       <c r="F80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H80">
         <v>0.20333999999999999</v>
@@ -3302,7 +3302,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B81">
         <v>3.87</v>
@@ -3317,10 +3317,10 @@
         <v>2.6589999999999998</v>
       </c>
       <c r="F81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H81">
         <v>0.20668</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B82">
         <v>3.91</v>
@@ -3352,10 +3352,10 @@
         <v>2.6802999999999999</v>
       </c>
       <c r="F82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H82">
         <v>0.20598</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B83">
         <v>3.95</v>
@@ -3387,10 +3387,10 @@
         <v>2.7016</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H83">
         <v>0.20383499999999999</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B84">
         <v>3.99</v>
@@ -3422,10 +3422,10 @@
         <v>2.7229000000000001</v>
       </c>
       <c r="F84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H84">
         <v>0.21723000000000001</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B85">
         <v>4.07</v>
@@ -3457,10 +3457,10 @@
         <v>2.7654999999999998</v>
       </c>
       <c r="F85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H85">
         <v>0.20962500000000001</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B86">
         <v>4.1100000000000003</v>
@@ -3492,10 +3492,10 @@
         <v>2.7867999999999999</v>
       </c>
       <c r="F86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H86">
         <v>0.20515</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B87">
         <v>4.1900000000000004</v>
@@ -3527,10 +3527,10 @@
         <v>2.8294999999999999</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H87">
         <v>0.22015999999999999</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B88">
         <v>4.2300000000000004</v>
@@ -3562,10 +3562,10 @@
         <v>2.8508</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H88">
         <v>0.22086</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B89">
         <v>4.2699999999999996</v>
@@ -3597,10 +3597,10 @@
         <v>2.8721000000000001</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H89">
         <v>0.21992999999999999</v>
@@ -3617,7 +3617,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B90">
         <v>0.47</v>
@@ -3632,10 +3632,10 @@
         <v>1.38</v>
       </c>
       <c r="F90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H90">
         <v>2.9141499999999999E-3</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B91">
         <v>0.51</v>
@@ -3667,10 +3667,10 @@
         <v>1.4013</v>
       </c>
       <c r="F91" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H91">
         <v>3.8137000000000002E-3</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B92">
         <v>0.55000000000000004</v>
@@ -3702,10 +3702,10 @@
         <v>1.4226000000000001</v>
       </c>
       <c r="F92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H92">
         <v>4.7936999999999997E-3</v>
@@ -3722,7 +3722,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B93">
         <v>0.59</v>
@@ -3737,10 +3737,10 @@
         <v>1.444</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H93">
         <v>6.3064999999999996E-3</v>
@@ -3757,7 +3757,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B94">
         <v>0.63</v>
@@ -3772,10 +3772,10 @@
         <v>1.4653</v>
       </c>
       <c r="F94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H94">
         <v>8.0704999999999995E-3</v>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B95">
         <v>0.67</v>
@@ -3807,10 +3807,10 @@
         <v>1.4865999999999999</v>
       </c>
       <c r="F95" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H95">
         <v>1.0814499999999999E-2</v>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B96">
         <v>0.71</v>
@@ -3842,10 +3842,10 @@
         <v>1.5079</v>
       </c>
       <c r="F96" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H96">
         <v>1.3381499999999999E-2</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B97">
         <v>0.75</v>
@@ -3877,10 +3877,10 @@
         <v>1.5291999999999999</v>
       </c>
       <c r="F97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H97">
         <v>1.6927999999999999E-2</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B98">
         <v>0.79</v>
@@ -3912,10 +3912,10 @@
         <v>1.5505</v>
       </c>
       <c r="F98" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H98">
         <v>2.0965000000000001E-2</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B99">
         <v>0.83</v>
@@ -3947,10 +3947,10 @@
         <v>1.5718000000000001</v>
       </c>
       <c r="F99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H99">
         <v>2.3571499999999999E-2</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B100">
         <v>0.87</v>
@@ -3982,10 +3982,10 @@
         <v>1.5931999999999999</v>
       </c>
       <c r="F100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H100">
         <v>2.5801999999999999E-2</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B101">
         <v>0.91</v>
@@ -4017,10 +4017,10 @@
         <v>1.6145</v>
       </c>
       <c r="F101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H101">
         <v>2.5701000000000002E-2</v>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B102">
         <v>0.95</v>
@@ -4052,10 +4052,10 @@
         <v>1.6357999999999999</v>
       </c>
       <c r="F102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H102">
         <v>2.4312E-2</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B103">
         <v>0.99</v>
@@ -4087,10 +4087,10 @@
         <v>1.6571</v>
       </c>
       <c r="F103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H103">
         <v>2.2428E-2</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B104">
         <v>1.03</v>
@@ -4122,10 +4122,10 @@
         <v>1.6783999999999999</v>
       </c>
       <c r="F104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H104">
         <v>2.0366499999999999E-2</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B105">
         <v>1.07</v>
@@ -4157,10 +4157,10 @@
         <v>1.6997</v>
       </c>
       <c r="F105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H105">
         <v>1.8354499999999999E-2</v>
@@ -4177,7 +4177,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B106">
         <v>1.1100000000000001</v>
@@ -4192,10 +4192,10 @@
         <v>1.7211000000000001</v>
       </c>
       <c r="F106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H106">
         <v>1.6482500000000001E-2</v>
@@ -4212,7 +4212,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B107">
         <v>1.1499999999999999</v>
@@ -4227,10 +4227,10 @@
         <v>1.7423999999999999</v>
       </c>
       <c r="F107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H107">
         <v>1.55245E-2</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B108">
         <v>1.19</v>
@@ -4262,10 +4262,10 @@
         <v>1.7637</v>
       </c>
       <c r="F108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H108">
         <v>1.5594500000000001E-2</v>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B109">
         <v>1.23</v>
@@ -4297,10 +4297,10 @@
         <v>1.7849999999999999</v>
       </c>
       <c r="F109" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H109">
         <v>1.6172499999999999E-2</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B110">
         <v>1.27</v>
@@ -4332,10 +4332,10 @@
         <v>1.8063</v>
       </c>
       <c r="F110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H110">
         <v>1.7364500000000001E-2</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B111">
         <v>1.31</v>
@@ -4367,10 +4367,10 @@
         <v>1.8275999999999999</v>
       </c>
       <c r="F111" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H111">
         <v>1.8450999999999999E-2</v>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B112">
         <v>1.35</v>
@@ -4402,10 +4402,10 @@
         <v>1.849</v>
       </c>
       <c r="F112" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H112">
         <v>2.0580000000000001E-2</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B113">
         <v>1.39</v>
@@ -4437,10 +4437,10 @@
         <v>1.8703000000000001</v>
       </c>
       <c r="F113" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H113">
         <v>2.2827E-2</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B114">
         <v>1.43</v>
@@ -4472,10 +4472,10 @@
         <v>1.8915999999999999</v>
       </c>
       <c r="F114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H114">
         <v>2.4795500000000002E-2</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B115">
         <v>1.47</v>
@@ -4507,10 +4507,10 @@
         <v>1.9129</v>
       </c>
       <c r="F115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H115">
         <v>2.64145E-2</v>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B116">
         <v>1.51</v>
@@ -4542,10 +4542,10 @@
         <v>1.9341999999999999</v>
       </c>
       <c r="F116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H116">
         <v>2.77915E-2</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B117">
         <v>1.55</v>
@@ -4577,10 +4577,10 @@
         <v>1.9555</v>
       </c>
       <c r="F117" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H117">
         <v>2.8861499999999998E-2</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B118">
         <v>1.59</v>
@@ -4612,10 +4612,10 @@
         <v>1.9767999999999999</v>
       </c>
       <c r="F118" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H118">
         <v>3.0308000000000002E-2</v>
@@ -4632,7 +4632,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B119">
         <v>1.63</v>
@@ -4647,10 +4647,10 @@
         <v>1.9982</v>
       </c>
       <c r="F119" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H119">
         <v>3.0974000000000002E-2</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B120">
         <v>1.67</v>
@@ -4682,10 +4682,10 @@
         <v>2.0194999999999999</v>
       </c>
       <c r="F120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H120">
         <v>3.23325E-2</v>
@@ -4702,7 +4702,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B121">
         <v>1.71</v>
@@ -4717,10 +4717,10 @@
         <v>2.0407999999999999</v>
       </c>
       <c r="F121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H121">
         <v>3.4284000000000002E-2</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B122">
         <v>1.75</v>
@@ -4752,10 +4752,10 @@
         <v>2.0621</v>
       </c>
       <c r="F122" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H122">
         <v>3.50665E-2</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B123">
         <v>1.79</v>
@@ -4787,10 +4787,10 @@
         <v>2.0834000000000001</v>
       </c>
       <c r="F123" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H123">
         <v>3.6135500000000001E-2</v>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B124">
         <v>1.83</v>
@@ -4822,10 +4822,10 @@
         <v>2.1046999999999998</v>
       </c>
       <c r="F124" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H124">
         <v>3.8108499999999997E-2</v>
@@ -4842,7 +4842,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B125">
         <v>1.87</v>
@@ -4857,10 +4857,10 @@
         <v>2.1261000000000001</v>
       </c>
       <c r="F125" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H125">
         <v>3.95415E-2</v>
@@ -4877,7 +4877,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B126">
         <v>1.91</v>
@@ -4892,10 +4892,10 @@
         <v>2.1474000000000002</v>
       </c>
       <c r="F126" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H126">
         <v>4.1395500000000002E-2</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B127">
         <v>1.95</v>
@@ -4927,10 +4927,10 @@
         <v>2.1686999999999999</v>
       </c>
       <c r="F127" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H127">
         <v>4.4366999999999997E-2</v>
@@ -4947,7 +4947,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B128">
         <v>1.99</v>
@@ -4962,10 +4962,10 @@
         <v>2.19</v>
       </c>
       <c r="F128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H128">
         <v>4.6605000000000001E-2</v>
@@ -4982,7 +4982,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B129">
         <v>2.0299999999999998</v>
@@ -4997,10 +4997,10 @@
         <v>2.2113</v>
       </c>
       <c r="F129" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H129">
         <v>4.9459999999999997E-2</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B130">
         <v>2.0699999999999998</v>
@@ -5032,10 +5032,10 @@
         <v>2.2326000000000001</v>
       </c>
       <c r="F130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H130">
         <v>5.1209999999999999E-2</v>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B131">
         <v>2.11</v>
@@ -5067,10 +5067,10 @@
         <v>2.254</v>
       </c>
       <c r="F131" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H131">
         <v>5.4385000000000003E-2</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B132">
         <v>2.15</v>
@@ -5102,10 +5102,10 @@
         <v>2.2753000000000001</v>
       </c>
       <c r="F132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G132" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H132">
         <v>5.6094999999999999E-2</v>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B133">
         <v>2.19</v>
@@ -5137,10 +5137,10 @@
         <v>2.2966000000000002</v>
       </c>
       <c r="F133" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G133" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H133">
         <v>5.8430000000000003E-2</v>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B134">
         <v>2.23</v>
@@ -5172,10 +5172,10 @@
         <v>2.3178999999999998</v>
       </c>
       <c r="F134" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H134">
         <v>6.1254999999999997E-2</v>
@@ -5192,7 +5192,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B135">
         <v>2.27</v>
@@ -5207,10 +5207,10 @@
         <v>2.3391999999999999</v>
       </c>
       <c r="F135" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H135">
         <v>6.3664999999999999E-2</v>
@@ -5227,7 +5227,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B136">
         <v>2.31</v>
@@ -5242,10 +5242,10 @@
         <v>2.3605</v>
       </c>
       <c r="F136" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H136">
         <v>6.4500000000000002E-2</v>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B137">
         <v>2.35</v>
@@ -5277,10 +5277,10 @@
         <v>2.3818000000000001</v>
       </c>
       <c r="F137" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H137">
         <v>6.7059999999999995E-2</v>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B138">
         <v>2.39</v>
@@ -5312,10 +5312,10 @@
         <v>2.4032</v>
       </c>
       <c r="F138" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G138" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H138">
         <v>6.9089999999999999E-2</v>
@@ -5332,7 +5332,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B139">
         <v>2.4300000000000002</v>
@@ -5347,10 +5347,10 @@
         <v>2.4245000000000001</v>
       </c>
       <c r="F139" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H139">
         <v>6.9379999999999997E-2</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B140">
         <v>2.4700000000000002</v>
@@ -5382,10 +5382,10 @@
         <v>2.4458000000000002</v>
       </c>
       <c r="F140" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H140">
         <v>7.2440000000000004E-2</v>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B141">
         <v>2.5099999999999998</v>
@@ -5417,10 +5417,10 @@
         <v>2.4670999999999998</v>
       </c>
       <c r="F141" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H141">
         <v>7.5740000000000002E-2</v>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B142">
         <v>2.5499999999999998</v>
@@ -5452,10 +5452,10 @@
         <v>2.4883999999999999</v>
       </c>
       <c r="F142" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G142" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H142">
         <v>7.7935000000000004E-2</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B143">
         <v>2.59</v>
@@ -5487,10 +5487,10 @@
         <v>2.5097</v>
       </c>
       <c r="F143" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H143">
         <v>7.9250000000000001E-2</v>
@@ -5507,7 +5507,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B144">
         <v>2.63</v>
@@ -5522,10 +5522,10 @@
         <v>2.5310999999999999</v>
       </c>
       <c r="F144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H144">
         <v>8.1134999999999999E-2</v>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B145">
         <v>2.67</v>
@@ -5557,10 +5557,10 @@
         <v>2.5524</v>
       </c>
       <c r="F145" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G145" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H145">
         <v>8.4970000000000004E-2</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B146">
         <v>2.71</v>
@@ -5592,10 +5592,10 @@
         <v>2.5737000000000001</v>
       </c>
       <c r="F146" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H146">
         <v>8.4964999999999999E-2</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B147">
         <v>2.75</v>
@@ -5627,10 +5627,10 @@
         <v>2.5950000000000002</v>
       </c>
       <c r="F147" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H147">
         <v>8.7529999999999997E-2</v>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B148">
         <v>2.79</v>
@@ -5662,10 +5662,10 @@
         <v>2.6162999999999998</v>
       </c>
       <c r="F148" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H148">
         <v>8.9795E-2</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B149">
         <v>2.83</v>
@@ -5697,10 +5697,10 @@
         <v>2.6375999999999999</v>
       </c>
       <c r="F149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H149">
         <v>9.1319999999999998E-2</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B150">
         <v>2.91</v>
@@ -5732,10 +5732,10 @@
         <v>2.6802999999999999</v>
       </c>
       <c r="F150" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H150">
         <v>9.6775E-2</v>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B151">
         <v>2.99</v>
@@ -5767,10 +5767,10 @@
         <v>2.7229000000000001</v>
       </c>
       <c r="F151" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G151" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H151">
         <v>0.101045</v>
@@ -5787,7 +5787,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B152">
         <v>3.03</v>
@@ -5802,10 +5802,10 @@
         <v>2.7442000000000002</v>
       </c>
       <c r="F152" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H152">
         <v>0.10123</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B153">
         <v>3.07</v>
@@ -5837,10 +5837,10 @@
         <v>2.7654999999999998</v>
       </c>
       <c r="F153" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H153">
         <v>0.10273500000000001</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B154">
         <v>3.11</v>
@@ -5872,10 +5872,10 @@
         <v>2.7867999999999999</v>
       </c>
       <c r="F154" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G154" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H154">
         <v>0.10682999999999999</v>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B155">
         <v>3.15</v>
@@ -5907,10 +5907,10 @@
         <v>2.8081999999999998</v>
       </c>
       <c r="F155" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H155">
         <v>0.10778500000000001</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B156">
         <v>3.19</v>
@@ -5942,10 +5942,10 @@
         <v>2.8294999999999999</v>
       </c>
       <c r="F156" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G156" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H156">
         <v>0.11047</v>
@@ -5962,7 +5962,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B157">
         <v>3.23</v>
@@ -5977,10 +5977,10 @@
         <v>2.8508</v>
       </c>
       <c r="F157" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H157">
         <v>0.11164499999999999</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B158">
         <v>3.27</v>
@@ -6012,10 +6012,10 @@
         <v>2.8721000000000001</v>
       </c>
       <c r="F158" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G158" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H158">
         <v>0.112775</v>
@@ -6032,7 +6032,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B159">
         <v>3.31</v>
@@ -6047,10 +6047,10 @@
         <v>2.8934000000000002</v>
       </c>
       <c r="F159" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G159" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H159">
         <v>0.11446000000000001</v>
@@ -6067,7 +6067,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B160">
         <v>3.35</v>
@@ -6082,10 +6082,10 @@
         <v>2.9146999999999998</v>
       </c>
       <c r="F160" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G160" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H160">
         <v>0.117245</v>
@@ -6102,7 +6102,7 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B161">
         <v>3.39</v>
@@ -6117,10 +6117,10 @@
         <v>2.9361000000000002</v>
       </c>
       <c r="F161" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G161" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H161">
         <v>0.11830499999999999</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B162">
         <v>3.43</v>
@@ -6152,10 +6152,10 @@
         <v>2.9573999999999998</v>
       </c>
       <c r="F162" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G162" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H162">
         <v>0.12121999999999999</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B163">
         <v>3.47</v>
@@ -6187,10 +6187,10 @@
         <v>2.9786999999999999</v>
       </c>
       <c r="F163" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G163" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H163">
         <v>0.12661500000000001</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B164">
         <v>3.51</v>
@@ -6222,10 +6222,10 @@
         <v>3</v>
       </c>
       <c r="F164" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G164" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H164">
         <v>0.126585</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B165">
         <v>3.55</v>
@@ -6257,10 +6257,10 @@
         <v>3.0213000000000001</v>
       </c>
       <c r="F165" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H165">
         <v>0.12665499999999999</v>
@@ -6277,7 +6277,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B166">
         <v>3.59</v>
@@ -6292,10 +6292,10 @@
         <v>3.0426000000000002</v>
       </c>
       <c r="F166" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G166" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H166">
         <v>0.12831000000000001</v>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B167">
         <v>3.63</v>
@@ -6327,10 +6327,10 @@
         <v>3.0640000000000001</v>
       </c>
       <c r="F167" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G167" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H167">
         <v>0.12988</v>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B168">
         <v>3.67</v>
@@ -6362,10 +6362,10 @@
         <v>3.0853000000000002</v>
       </c>
       <c r="F168" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G168" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H168">
         <v>0.13072500000000001</v>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B169">
         <v>3.71</v>
@@ -6397,10 +6397,10 @@
         <v>3.1065999999999998</v>
       </c>
       <c r="F169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G169" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H169">
         <v>0.13079499999999999</v>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B170">
         <v>3.75</v>
@@ -6432,10 +6432,10 @@
         <v>3.1278999999999999</v>
       </c>
       <c r="F170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H170">
         <v>0.136765</v>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B171">
         <v>3.79</v>
@@ -6467,10 +6467,10 @@
         <v>3.1492</v>
       </c>
       <c r="F171" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G171" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H171">
         <v>0.134355</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B172">
         <v>3.83</v>
@@ -6502,10 +6502,10 @@
         <v>3.1705000000000001</v>
       </c>
       <c r="F172" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G172" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H172">
         <v>0.14304500000000001</v>
@@ -6522,7 +6522,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B173">
         <v>3.87</v>
@@ -6537,10 +6537,10 @@
         <v>3.1918000000000002</v>
       </c>
       <c r="F173" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G173" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H173">
         <v>0.141015</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B174">
         <v>3.91</v>
@@ -6572,10 +6572,10 @@
         <v>3.2132000000000001</v>
       </c>
       <c r="F174" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G174" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H174">
         <v>0.13875499999999999</v>
@@ -6592,7 +6592,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B175">
         <v>3.95</v>
@@ -6607,10 +6607,10 @@
         <v>3.2345000000000002</v>
       </c>
       <c r="F175" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G175" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H175">
         <v>0.13858000000000001</v>
@@ -6627,7 +6627,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B176">
         <v>3.99</v>
@@ -6642,10 +6642,10 @@
         <v>3.2557999999999998</v>
       </c>
       <c r="F176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G176" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H176">
         <v>0.14299999999999999</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B177">
         <v>4.03</v>
@@ -6677,10 +6677,10 @@
         <v>3.2770999999999999</v>
       </c>
       <c r="F177" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G177" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H177">
         <v>0.14323</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B178">
         <v>4.07</v>
@@ -6712,10 +6712,10 @@
         <v>3.2984</v>
       </c>
       <c r="F178" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G178" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H178">
         <v>0.14907000000000001</v>
@@ -6732,7 +6732,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B179">
         <v>4.1100000000000003</v>
@@ -6747,10 +6747,10 @@
         <v>3.3197000000000001</v>
       </c>
       <c r="F179" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G179" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H179">
         <v>0.149645</v>
@@ -6767,7 +6767,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B180">
         <v>4.1500000000000004</v>
@@ -6782,10 +6782,10 @@
         <v>3.3411</v>
       </c>
       <c r="F180" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H180">
         <v>0.15362999999999999</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B181">
         <v>4.1900000000000004</v>
@@ -6817,10 +6817,10 @@
         <v>3.3624000000000001</v>
       </c>
       <c r="F181" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G181" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H181">
         <v>0.15179000000000001</v>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B182">
         <v>4.3099999999999996</v>
@@ -6852,10 +6852,10 @@
         <v>3.4262999999999999</v>
       </c>
       <c r="F182" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H182">
         <v>0.16092000000000001</v>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B183">
         <v>4.3499999999999996</v>
@@ -6887,10 +6887,10 @@
         <v>3.4476</v>
       </c>
       <c r="F183" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H183">
         <v>0.161775</v>
@@ -6907,7 +6907,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B184">
         <v>4.3899999999999997</v>
@@ -6922,10 +6922,10 @@
         <v>3.4689999999999999</v>
       </c>
       <c r="F184" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G184" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H184">
         <v>0.16581499999999999</v>
@@ -6942,7 +6942,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B185">
         <v>4.43</v>
@@ -6957,10 +6957,10 @@
         <v>3.4903</v>
       </c>
       <c r="F185" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G185" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H185">
         <v>0.16333</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B186">
         <v>0.43</v>
@@ -6992,10 +6992,10 @@
         <v>1.8915999999999999</v>
       </c>
       <c r="F186" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G186" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H186">
         <v>1.8334E-3</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B187">
         <v>0.47</v>
@@ -7027,10 +7027,10 @@
         <v>1.9129</v>
       </c>
       <c r="F187" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G187" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H187">
         <v>1.6096000000000001E-3</v>
@@ -7047,7 +7047,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B188">
         <v>0.51</v>
@@ -7062,10 +7062,10 @@
         <v>1.9341999999999999</v>
       </c>
       <c r="F188" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G188" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H188">
         <v>2.5190500000000001E-3</v>
@@ -7082,7 +7082,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B189">
         <v>0.59</v>
@@ -7097,10 +7097,10 @@
         <v>1.9767999999999999</v>
       </c>
       <c r="F189" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H189">
         <v>4.2987499999999996E-3</v>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B190">
         <v>0.63</v>
@@ -7132,10 +7132,10 @@
         <v>1.9982</v>
       </c>
       <c r="F190" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H190">
         <v>5.0569999999999999E-3</v>
@@ -7152,7 +7152,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B191">
         <v>0.67</v>
@@ -7167,10 +7167,10 @@
         <v>2.0194999999999999</v>
       </c>
       <c r="F191" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G191" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H191">
         <v>6.2005000000000003E-3</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B192">
         <v>0.71</v>
@@ -7202,10 +7202,10 @@
         <v>2.0407999999999999</v>
       </c>
       <c r="F192" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G192" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H192">
         <v>7.7840000000000001E-3</v>
@@ -7222,7 +7222,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B193">
         <v>0.79</v>
@@ -7237,10 +7237,10 @@
         <v>2.0834000000000001</v>
       </c>
       <c r="F193" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G193" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H193">
         <v>9.9129999999999999E-3</v>
@@ -7257,7 +7257,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B194">
         <v>0.83</v>
@@ -7272,10 +7272,10 @@
         <v>2.1046999999999998</v>
       </c>
       <c r="F194" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G194" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H194">
         <v>1.1037999999999999E-2</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B195">
         <v>0.87</v>
@@ -7307,10 +7307,10 @@
         <v>2.1261000000000001</v>
       </c>
       <c r="F195" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G195" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H195">
         <v>1.1754000000000001E-2</v>
@@ -7327,7 +7327,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B196">
         <v>0.91</v>
@@ -7342,10 +7342,10 @@
         <v>2.1474000000000002</v>
       </c>
       <c r="F196" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G196" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H196">
         <v>1.2748499999999999E-2</v>
@@ -7362,7 +7362,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B197">
         <v>0.99</v>
@@ -7377,10 +7377,10 @@
         <v>2.19</v>
       </c>
       <c r="F197" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G197" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H197">
         <v>1.1547999999999999E-2</v>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B198">
         <v>1.03</v>
@@ -7412,10 +7412,10 @@
         <v>2.2113</v>
       </c>
       <c r="F198" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H198">
         <v>1.10635E-2</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B199">
         <v>1.07</v>
@@ -7447,10 +7447,10 @@
         <v>2.2326000000000001</v>
       </c>
       <c r="F199" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H199">
         <v>1.0284E-2</v>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B200">
         <v>1.1100000000000001</v>
@@ -7482,10 +7482,10 @@
         <v>2.254</v>
       </c>
       <c r="F200" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G200" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H200">
         <v>9.6255000000000004E-3</v>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B201">
         <v>1.19</v>
@@ -7517,10 +7517,10 @@
         <v>2.2966000000000002</v>
       </c>
       <c r="F201" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G201" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H201">
         <v>9.6244999999999994E-3</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B202">
         <v>1.23</v>
@@ -7552,10 +7552,10 @@
         <v>2.3178999999999998</v>
       </c>
       <c r="F202" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G202" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H202">
         <v>9.8034999999999997E-3</v>
@@ -7572,7 +7572,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B203">
         <v>1.27</v>
@@ -7587,10 +7587,10 @@
         <v>2.3391999999999999</v>
       </c>
       <c r="F203" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G203" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H203">
         <v>1.0267E-2</v>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B204">
         <v>1.31</v>
@@ -7622,10 +7622,10 @@
         <v>2.3605</v>
       </c>
       <c r="F204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G204" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H204">
         <v>1.0943E-2</v>
@@ -7642,7 +7642,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B205">
         <v>1.35</v>
@@ -7657,10 +7657,10 @@
         <v>2.3818000000000001</v>
       </c>
       <c r="F205" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G205" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H205">
         <v>1.19405E-2</v>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B206">
         <v>1.39</v>
@@ -7692,10 +7692,10 @@
         <v>2.4032</v>
       </c>
       <c r="F206" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G206" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H206">
         <v>1.2683E-2</v>
@@ -7712,7 +7712,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B207">
         <v>1.43</v>
@@ -7727,10 +7727,10 @@
         <v>2.4245000000000001</v>
       </c>
       <c r="F207" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G207" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H207">
         <v>1.31355E-2</v>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B208">
         <v>1.47</v>
@@ -7762,10 +7762,10 @@
         <v>2.4458000000000002</v>
       </c>
       <c r="F208" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G208" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H208">
         <v>1.4234999999999999E-2</v>
@@ -7782,7 +7782,7 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B209">
         <v>1.51</v>
@@ -7797,10 +7797,10 @@
         <v>2.4670999999999998</v>
       </c>
       <c r="F209" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G209" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H209">
         <v>1.5570000000000001E-2</v>
@@ -7817,7 +7817,7 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B210">
         <v>1.55</v>
@@ -7832,10 +7832,10 @@
         <v>2.4883999999999999</v>
       </c>
       <c r="F210" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G210" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H210">
         <v>1.58435E-2</v>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B211">
         <v>1.59</v>
@@ -7867,10 +7867,10 @@
         <v>2.5097</v>
       </c>
       <c r="F211" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G211" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H211">
         <v>1.70125E-2</v>
@@ -7887,7 +7887,7 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B212">
         <v>1.67</v>
@@ -7902,10 +7902,10 @@
         <v>2.5524</v>
       </c>
       <c r="F212" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G212" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H212">
         <v>1.9767E-2</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B213">
         <v>1.71</v>
@@ -7937,10 +7937,10 @@
         <v>2.5737000000000001</v>
       </c>
       <c r="F213" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G213" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H213">
         <v>1.9524E-2</v>
@@ -7957,7 +7957,7 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B214">
         <v>1.75</v>
@@ -7972,10 +7972,10 @@
         <v>2.5950000000000002</v>
       </c>
       <c r="F214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G214" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H214">
         <v>2.2235000000000001E-2</v>
@@ -7992,7 +7992,7 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B215">
         <v>1.79</v>
@@ -8007,10 +8007,10 @@
         <v>2.6162999999999998</v>
       </c>
       <c r="F215" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G215" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H215">
         <v>2.2997E-2</v>
@@ -8027,7 +8027,7 @@
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B216">
         <v>1.83</v>
@@ -8042,10 +8042,10 @@
         <v>2.6375999999999999</v>
       </c>
       <c r="F216" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G216" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H216">
         <v>2.2582999999999999E-2</v>
@@ -8062,7 +8062,7 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B217">
         <v>1.87</v>
@@ -8077,10 +8077,10 @@
         <v>2.6589999999999998</v>
       </c>
       <c r="F217" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G217" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H217">
         <v>2.3706000000000001E-2</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B218">
         <v>1.91</v>
@@ -8112,10 +8112,10 @@
         <v>2.6802999999999999</v>
       </c>
       <c r="F218" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G218" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H218">
         <v>2.51965E-2</v>
@@ -8132,7 +8132,7 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B219">
         <v>1.95</v>
@@ -8147,10 +8147,10 @@
         <v>2.7016</v>
       </c>
       <c r="F219" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G219" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H219">
         <v>2.5912500000000002E-2</v>
@@ -8167,7 +8167,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B220">
         <v>1.99</v>
@@ -8182,10 +8182,10 @@
         <v>2.7229000000000001</v>
       </c>
       <c r="F220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G220" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H220">
         <v>2.7835499999999999E-2</v>
@@ -8202,7 +8202,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B221">
         <v>2.0299999999999998</v>
@@ -8217,10 +8217,10 @@
         <v>2.7442000000000002</v>
       </c>
       <c r="F221" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G221" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H221">
         <v>3.1689000000000002E-2</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B222">
         <v>2.0699999999999998</v>
@@ -8252,10 +8252,10 @@
         <v>2.7654999999999998</v>
       </c>
       <c r="F222" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G222" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H222">
         <v>3.1385499999999997E-2</v>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B223">
         <v>2.11</v>
@@ -8287,10 +8287,10 @@
         <v>2.7867999999999999</v>
       </c>
       <c r="F223" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G223" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H223">
         <v>3.2794999999999998E-2</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B224">
         <v>2.15</v>
@@ -8322,10 +8322,10 @@
         <v>2.8081999999999998</v>
       </c>
       <c r="F224" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G224" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H224">
         <v>3.5089000000000002E-2</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B225">
         <v>2.19</v>
@@ -8357,10 +8357,10 @@
         <v>2.8294999999999999</v>
       </c>
       <c r="F225" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G225" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H225">
         <v>3.5931499999999998E-2</v>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B226">
         <v>2.27</v>
@@ -8392,10 +8392,10 @@
         <v>2.8721000000000001</v>
       </c>
       <c r="F226" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G226" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H226">
         <v>3.9183000000000003E-2</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B227">
         <v>2.31</v>
@@ -8427,10 +8427,10 @@
         <v>2.8934000000000002</v>
       </c>
       <c r="F227" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G227" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H227">
         <v>4.0516000000000003E-2</v>
@@ -8447,7 +8447,7 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B228">
         <v>2.35</v>
@@ -8462,10 +8462,10 @@
         <v>2.9146999999999998</v>
       </c>
       <c r="F228" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G228" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H228">
         <v>4.0507000000000001E-2</v>
@@ -8482,7 +8482,7 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B229">
         <v>2.39</v>
@@ -8497,10 +8497,10 @@
         <v>2.9361000000000002</v>
       </c>
       <c r="F229" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G229" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H229">
         <v>4.2518500000000001E-2</v>
@@ -8517,7 +8517,7 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B230">
         <v>2.4300000000000002</v>
@@ -8532,10 +8532,10 @@
         <v>2.9573999999999998</v>
       </c>
       <c r="F230" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G230" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H230">
         <v>4.3478999999999997E-2</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B231">
         <v>2.4700000000000002</v>
@@ -8567,10 +8567,10 @@
         <v>2.9786999999999999</v>
       </c>
       <c r="F231" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G231" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H231">
         <v>4.4926000000000001E-2</v>
@@ -8587,7 +8587,7 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B232">
         <v>2.5099999999999998</v>
@@ -8602,10 +8602,10 @@
         <v>3</v>
       </c>
       <c r="F232" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G232" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H232">
         <v>4.7334500000000002E-2</v>
@@ -8622,7 +8622,7 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B233">
         <v>2.5499999999999998</v>
@@ -8637,10 +8637,10 @@
         <v>3.0213000000000001</v>
       </c>
       <c r="F233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G233" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H233">
         <v>4.7036500000000002E-2</v>
@@ -8657,7 +8657,7 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B234">
         <v>2.59</v>
@@ -8672,10 +8672,10 @@
         <v>3.0426000000000002</v>
       </c>
       <c r="F234" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G234" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H234">
         <v>5.0290000000000001E-2</v>
@@ -8692,7 +8692,7 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B235">
         <v>2.63</v>
@@ -8707,10 +8707,10 @@
         <v>3.0640000000000001</v>
       </c>
       <c r="F235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G235" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H235">
         <v>5.1200000000000002E-2</v>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B236">
         <v>2.67</v>
@@ -8742,10 +8742,10 @@
         <v>3.0853000000000002</v>
       </c>
       <c r="F236" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G236" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H236">
         <v>5.3525000000000003E-2</v>
@@ -8762,7 +8762,7 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B237">
         <v>2.71</v>
@@ -8777,10 +8777,10 @@
         <v>3.1065999999999998</v>
       </c>
       <c r="F237" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G237" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H237">
         <v>5.3905000000000002E-2</v>
@@ -8797,7 +8797,7 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B238">
         <v>2.75</v>
@@ -8812,10 +8812,10 @@
         <v>3.1278999999999999</v>
       </c>
       <c r="F238" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G238" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H238">
         <v>5.645E-2</v>
@@ -8832,7 +8832,7 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B239">
         <v>2.79</v>
@@ -8847,10 +8847,10 @@
         <v>3.1492</v>
       </c>
       <c r="F239" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G239" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H239">
         <v>5.7584999999999997E-2</v>
@@ -8867,7 +8867,7 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B240">
         <v>2.83</v>
@@ -8882,10 +8882,10 @@
         <v>3.1705000000000001</v>
       </c>
       <c r="F240" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G240" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H240">
         <v>6.1475000000000002E-2</v>
@@ -8902,7 +8902,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B241">
         <v>2.87</v>
@@ -8917,10 +8917,10 @@
         <v>3.1918000000000002</v>
       </c>
       <c r="F241" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G241" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H241">
         <v>6.3365000000000005E-2</v>
@@ -8937,7 +8937,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B242">
         <v>2.91</v>
@@ -8952,10 +8952,10 @@
         <v>3.2132000000000001</v>
       </c>
       <c r="F242" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G242" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H242">
         <v>6.3795000000000004E-2</v>
@@ -8972,7 +8972,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B243">
         <v>2.95</v>
@@ -8987,10 +8987,10 @@
         <v>3.2345000000000002</v>
       </c>
       <c r="F243" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G243" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H243">
         <v>6.268E-2</v>
@@ -9007,7 +9007,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B244">
         <v>2.99</v>
@@ -9022,10 +9022,10 @@
         <v>3.2557999999999998</v>
       </c>
       <c r="F244" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G244" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H244">
         <v>6.472E-2</v>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B245">
         <v>3.03</v>
@@ -9057,10 +9057,10 @@
         <v>3.2770999999999999</v>
       </c>
       <c r="F245" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G245" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H245">
         <v>6.9105E-2</v>
@@ -9077,7 +9077,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B246">
         <v>3.07</v>
@@ -9092,10 +9092,10 @@
         <v>3.2984</v>
       </c>
       <c r="F246" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G246" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H246">
         <v>6.4894999999999994E-2</v>
@@ -9112,7 +9112,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B247">
         <v>3.15</v>
@@ -9127,10 +9127,10 @@
         <v>3.3411</v>
       </c>
       <c r="F247" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G247" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H247">
         <v>6.8294999999999995E-2</v>
@@ -9147,7 +9147,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B248">
         <v>3.19</v>
@@ -9162,10 +9162,10 @@
         <v>3.3624000000000001</v>
       </c>
       <c r="F248" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G248" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H248">
         <v>6.9684999999999997E-2</v>
@@ -9182,7 +9182,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B249">
         <v>3.23</v>
@@ -9197,10 +9197,10 @@
         <v>3.3837000000000002</v>
       </c>
       <c r="F249" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G249" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H249">
         <v>7.1654999999999996E-2</v>
@@ -9217,7 +9217,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B250">
         <v>3.27</v>
@@ -9232,10 +9232,10 @@
         <v>3.4049999999999998</v>
       </c>
       <c r="F250" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G250" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H250">
         <v>7.0980000000000001E-2</v>
@@ -9252,7 +9252,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B251">
         <v>3.31</v>
@@ -9267,10 +9267,10 @@
         <v>3.4262999999999999</v>
       </c>
       <c r="F251" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G251" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H251">
         <v>7.9680000000000001E-2</v>
@@ -9287,7 +9287,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B252">
         <v>3.35</v>
@@ -9302,10 +9302,10 @@
         <v>3.4476</v>
       </c>
       <c r="F252" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G252" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H252">
         <v>7.9704999999999998E-2</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B253">
         <v>3.39</v>
@@ -9337,10 +9337,10 @@
         <v>3.4689999999999999</v>
       </c>
       <c r="F253" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G253" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H253">
         <v>8.2195000000000004E-2</v>
@@ -9357,7 +9357,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B254">
         <v>3.43</v>
@@ -9372,10 +9372,10 @@
         <v>3.4903</v>
       </c>
       <c r="F254" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G254" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H254">
         <v>7.9339999999999994E-2</v>
@@ -9392,7 +9392,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B255">
         <v>3.47</v>
@@ -9407,10 +9407,10 @@
         <v>3.5116000000000001</v>
       </c>
       <c r="F255" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G255" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H255">
         <v>8.0274999999999999E-2</v>
@@ -9427,7 +9427,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B256">
         <v>3.51</v>
@@ -9442,10 +9442,10 @@
         <v>3.5329000000000002</v>
       </c>
       <c r="F256" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G256" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H256">
         <v>8.387E-2</v>
@@ -9462,7 +9462,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B257">
         <v>3.55</v>
@@ -9477,10 +9477,10 @@
         <v>3.5541999999999998</v>
       </c>
       <c r="F257" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G257" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H257">
         <v>8.6165000000000005E-2</v>
@@ -9497,7 +9497,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B258">
         <v>3.59</v>
@@ -9512,10 +9512,10 @@
         <v>3.5754999999999999</v>
       </c>
       <c r="F258" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G258" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H258">
         <v>8.6715E-2</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B259">
         <v>3.63</v>
@@ -9547,10 +9547,10 @@
         <v>3.5968</v>
       </c>
       <c r="F259" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G259" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H259">
         <v>9.1600000000000001E-2</v>
